--- a/classification-systems/nzlum/build/management_practices.xlsx
+++ b/classification-systems/nzlum/build/management_practices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Collections" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collections" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,12 +1121,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A42"/>
     <mergeCell ref="A43:A45"/>
     <mergeCell ref="A46:A50"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A36:A42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
